--- a/data/trans_camb/P1403-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1403-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,98</t>
+          <t>8,91</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,46</t>
+          <t>15,16</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14,08</t>
+          <t>12,78</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,09; 13,3</t>
+          <t>4,72; 12,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 8,5</t>
+          <t>-0,09; 8,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,19; 14,43</t>
+          <t>4,65; 14,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 12,56</t>
+          <t>5,02; 12,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 8,68</t>
+          <t>0,54; 8,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,67; 20,14</t>
+          <t>11,52; 18,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,48; 12,4</t>
+          <t>6,48; 12,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 7,48</t>
+          <t>1,44; 7,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 17,17</t>
+          <t>9,95; 15,53</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>42,23%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,12; 53,9</t>
+          <t>16,83; 53,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 35,49</t>
+          <t>-0,17; 37,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,3; 60,01</t>
+          <t>16,5; 57,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,73; 39,59</t>
+          <t>14,63; 40,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 27,13</t>
+          <t>1,52; 27,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,17; 62,98</t>
+          <t>32,91; 59,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,71; 42,64</t>
+          <t>20,54; 41,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 25,72</t>
+          <t>4,54; 24,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,3; 58,65</t>
+          <t>31,59; 53,95</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,17</t>
+          <t>8,69</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,43</t>
+          <t>7,05</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,75</t>
+          <t>7,88</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,37</t>
+          <t>0,91; 4,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,76</t>
+          <t>2,11; 5,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 9,63</t>
+          <t>6,61; 10,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 3,58</t>
+          <t>-0,1; 3,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,34</t>
+          <t>2,51; 6,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 35,26</t>
+          <t>5,22; 8,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,47</t>
+          <t>0,92; 3,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,46</t>
+          <t>2,86; 5,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 24,32</t>
+          <t>6,62; 9,18</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102,31%</t>
+          <t>124,04%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>220,02%</t>
+          <t>107,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>158,36%</t>
+          <t>116,01%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,34; 70,21</t>
+          <t>11,36; 75,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,15; 94,13</t>
+          <t>25,67; 94,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,35; 152,31</t>
+          <t>81,36; 176,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 62,0</t>
+          <t>-1,67; 64,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,41; 110,55</t>
+          <t>34,44; 113,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,16; 599,38</t>
+          <t>67,99; 155,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,29; 55,58</t>
+          <t>12,38; 57,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,57; 87,98</t>
+          <t>38,61; 90,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>89,11; 396,96</t>
+          <t>87,15; 150,67</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,06</t>
+          <t>10,09</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,33</t>
+          <t>5,79</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,61</t>
+          <t>7,84</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 5,26</t>
+          <t>-1,52; 5,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 6,64</t>
+          <t>-0,28; 6,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 13,56</t>
+          <t>6,6; 13,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,48</t>
+          <t>-2,53; 4,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 3,27</t>
+          <t>-3,5; 3,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,86</t>
+          <t>2,87; 8,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 4,24</t>
+          <t>-0,95; 3,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 4,19</t>
+          <t>-0,66; 3,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 9,67</t>
+          <t>5,64; 10,12</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141,44%</t>
+          <t>141,76%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>116,72%</t>
+          <t>120,22%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,18; 95,71</t>
+          <t>-19,16; 97,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 121,98</t>
+          <t>-5,02; 121,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,42; 235,14</t>
+          <t>69,54; 246,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-33,98; 102,19</t>
+          <t>-35,08; 94,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,13; 76,28</t>
+          <t>-45,2; 72,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,3; 180,27</t>
+          <t>36,25; 193,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 74,98</t>
+          <t>-12,98; 72,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 77,26</t>
+          <t>-9,21; 72,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>63,16; 185,75</t>
+          <t>71,27; 194,93</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,96</t>
+          <t>6,13</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,24</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,67</t>
+          <t>5,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,65</t>
+          <t>2,0; 5,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,86</t>
+          <t>0,33; 3,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 7,07</t>
+          <t>4,21; 7,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,96</t>
+          <t>2,18; 6,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,75</t>
+          <t>-1,02; 2,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,07; 23,31</t>
+          <t>2,39; 5,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,23</t>
+          <t>2,62; 5,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,72</t>
+          <t>0,15; 2,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 14,16</t>
+          <t>3,78; 6,19</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,35; 46,22</t>
+          <t>14,45; 45,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,77; 31,62</t>
+          <t>2,37; 31,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,69; 56,81</t>
+          <t>30,18; 63,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,47; 37,02</t>
+          <t>12,26; 38,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 17,13</t>
+          <t>-5,78; 16,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,19; 141,18</t>
+          <t>13,32; 35,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,28; 36,88</t>
+          <t>16,79; 35,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 18,9</t>
+          <t>0,93; 18,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21,91; 96,1</t>
+          <t>23,82; 42,99</t>
         </is>
       </c>
     </row>
